--- a/ksoft_old/docs/records/Import_Expense_Records_CD2565.xlsx
+++ b/ksoft_old/docs/records/Import_Expense_Records_CD2565.xlsx
@@ -1871,13 +1871,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A354AA-DA56-49C6-8466-589E3A686817}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFBC6C6D-A2A1-4487-B864-704917F31828}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C910CFEA-3B45-4543-BF88-6C9A4849D60A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753D14F8-217A-4C24-8575-9B9F62AED14E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DCA4FA2-2195-4C9F-A58A-6975A0548FC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0994AA0F-6A5A-4997-AC96-F6FC3C280070}"/>
 </file>
--- a/ksoft_old/docs/records/Import_Expense_Records_CD2565.xlsx
+++ b/ksoft_old/docs/records/Import_Expense_Records_CD2565.xlsx
@@ -1871,13 +1871,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFBC6C6D-A2A1-4487-B864-704917F31828}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB8929E-B7F8-4543-80B1-C8D5F8C06F8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753D14F8-217A-4C24-8575-9B9F62AED14E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AED393-66A7-442E-B59F-0CE8D1ED0634}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0994AA0F-6A5A-4997-AC96-F6FC3C280070}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82846B1E-80B6-491A-8DA8-67027EC2FE57}"/>
 </file>
--- a/ksoft_old/docs/records/Import_Expense_Records_CD2565.xlsx
+++ b/ksoft_old/docs/records/Import_Expense_Records_CD2565.xlsx
@@ -1871,13 +1871,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB8929E-B7F8-4543-80B1-C8D5F8C06F8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9A354AA-DA56-49C6-8466-589E3A686817}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AED393-66A7-442E-B59F-0CE8D1ED0634}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C910CFEA-3B45-4543-BF88-6C9A4849D60A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82846B1E-80B6-491A-8DA8-67027EC2FE57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DCA4FA2-2195-4C9F-A58A-6975A0548FC5}"/>
 </file>